--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
@@ -50,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,50 +434,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>challenge_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>attack_intensity_baserate</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>attack_show_time</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>road_num</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>road_length</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fight_scene_ids</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>drop_crystal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>reward_crystal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>reward_equip_rarity</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>reward_exp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -501,34 +506,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
@@ -536,15 +541,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -568,50 +578,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>强度倍率(敌人HP/护甲/攻击力×该值;0或不配按1)</t>
+          <t>挑战类型(0=普通挑战;1=BOSS挑战,通关宝箱奖励翻倍:装备件数x2/魔晶数量x2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>强度倍率(敌人HP/护甲/攻击力×该值;单值=全难度共用,或与难度列表等长的逗号分隔逐难度值;0或不配按1)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>进攻总时间(秒,100只怪在此时间内出完)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>道路数量(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>道路长度(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>战斗场景列表(用,分割;随机其一)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>击杀掉落魔晶</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>奖励-每箱魔晶(单个数x或范围x-y)</t>
+          <t>击杀掉落魔晶(单值=全难度共用,或与难度列表等长的逗号分隔逐难度值)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>奖励-装备稀有度</t>
+          <t>奖励-每箱魔晶(每档x或x-y;多档与难度列表等长的逗号分隔逐难度值)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>通关经验(阵容每只)</t>
+          <t>奖励-装备稀有度(单值=全难度共用,或与难度列表等长的逗号分隔逐难度值)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>通关经验(阵容每只;单值=全难度共用,或与难度列表等长的逗号分隔逐难度值)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -628,47 +643,58 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1,1.25,1.5</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>300-450</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>50</v>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>100-150,200-250,300-350</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1,1,2</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>挑战100勇士-难度1-5</t>
+          <t>10,20,30</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>挑战100勇士-冒险者</t>
         </is>
       </c>
     </row>
@@ -678,52 +704,1779 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1040010001,1020010001,1030010001,1030020001,1030030001,1030040001,1020020002,1020030002</t>
+          <t>1010020002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>4,5,6</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.75,2,2.5</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,5,6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>400-450,500-550,600-650</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,2,3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>40,50,60</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>挑战100勇士-持盾战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1020010001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.25,1.5,1.75,2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>200-250,300-350,400-450,500-550</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1,2,2,2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>20,30,40,50</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>挑战100勇士-弓箭手</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1020020002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>6,7,8,9,10</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>120</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>5-10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>10001,20001</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>挑战100勇士-强弓手</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1020030002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>挑战100勇士-连射手</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>6</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1800-1950</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>400</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>挑战100勇士-难度6-10</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1030010001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.5,1.75,2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>300-350,400-450,500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,2,2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>30,40,50,60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-魔法师（火）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1030020001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.5,1.75,2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>300-350,400-450,500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,2,2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>30,40,50,60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-魔法师（水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1030030001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>50,60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-魔法师（冰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1030040001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50,60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-魔法师（雷）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1031050002</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,4.5</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>90,100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>挑战100勇士-骷髅召唤师-小兵（无BOSS技能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1031080002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1000-1200</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>挑战100勇士-牧师</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1040010001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.75,2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>400-450,500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2,2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>40,50,60,70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>挑战100勇士-盗贼</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1041010002</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>挑战100勇士-大剑战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1041020002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10001,20001</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>70,80,90,100</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>挑战100勇士-大盾战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1010020001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1,1.25</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>100-150,200-250</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>50,100</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>挑战100勇士-持盾战士-Boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1020020001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.25,1.5,1.75,2</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>200-250,300-350,400-450,500-550</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1,2,2,2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>100,150,200,250</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>挑战100勇士-强弓手-Boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1020030001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.25,1.5,1.75,2</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>200-250,300-350,400-450,500-550</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1,2,2,2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>100,150,200,250</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>挑战100勇士-连射手-Boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1031010001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.5,1.75,2,2.5,3,3.5</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>300-350,400-450,500-550,600-650,700-750,800-850</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2,2,2,3,3,3</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>150,200,250,300,350,400</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-大魔法师（火）-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1031010002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4,4.5</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>450,500</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>挑战100勇士-大魔导师（火冰水雷四系技能随机替代普攻,无普攻）-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1031020001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.5,1.75,2,2.5,3,3.5</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>300-350,400-450,500-550,600-650,700-750,800-850</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2,2,2,3,3,3</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>150,200,250,300,350,400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-大魔法师（水）-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1031030001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2,2.5,3,3.5</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>60</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>500-550,600-650,700-750,800-850</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2,3,3,3</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>250,300,350,400</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-大魔法师（冰）-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1031040001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2,2.5,3,3.5</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>60</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>500-550,600-650,700-750,800-850</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2,3,3,3</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>250,300,350,400</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>挑战100勇士-人类-大魔法师（雷）-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1031050001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>350,400,450,500</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>挑战100勇士-骷髅召唤师-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1031080001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8,9,10</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8,9,10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3,4,4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>400,450,500</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>挑战100勇士-神官-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1041010001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.75,2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>400-450,500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2,2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>200,250,300,350,400,450,500</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>挑战100勇士-大剑战士-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1041010003</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1000-1200</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>挑战100勇士-勇者(BOSS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1041020001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.75,2,2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>400-450,500-550,600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2,2,3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>200,250,300,350,400,450,500</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>挑战100勇士-大盾战士-BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1041030001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2.5,3,3.5,4,4.5</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>600-650,700-750,800-850,900-950,1000-1200</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>3,3,3,4,4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>300,350,400,450,500</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>挑战100勇士-长枪骑士-BOSS</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10,20,30</t>
+          <t>20,40,60</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40,50,60</t>
+          <t>80,100,120</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20,30,40,50</t>
+          <t>40,60,80,100</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>60,70,80,90,100</t>
+          <t>120,140,160,180,200</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>60,70,80,90,100</t>
+          <t>120,140,160,180,200</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>30,40,50,60,70,80,90,100</t>
+          <t>60,80,100,120,140,160,180,200</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>30,40,50,60,70,80,90,100</t>
+          <t>60,80,100,120,140,160,180,200</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>50,60,70,80,90,100</t>
+          <t>100,120,140,160,180,200</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>50,60,70,80,90,100</t>
+          <t>100,120,140,160,180,200</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>90,100</t>
+          <t>180,200</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>40,50,60,70,80,90,100</t>
+          <t>80,100,120,140,160,180,200</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>70,80,90,100</t>
+          <t>140,160,180,200</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>70,80,90,100</t>
+          <t>140,160,180,200</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>50,100</t>
+          <t>100,200</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>100,150,200,250</t>
+          <t>200,300,400,500</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>100,150,200,250</t>
+          <t>200,300,400,500</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>150,200,250,300,350,400</t>
+          <t>300,400,500,600,700,800</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>450,500</t>
+          <t>900,1000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>150,200,250,300,350,400</t>
+          <t>300,400,500,600,700,800</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>250,300,350,400</t>
+          <t>500,600,700,800</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>250,300,350,400</t>
+          <t>500,600,700,800</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>350,400,450,500</t>
+          <t>700,800,900,1000</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>400,450,500</t>
+          <t>800,900,1000</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>200,250,300,350,400,450,500</t>
+          <t>400,500,600,700,800,900,1000</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>200,250,300,350,400,450,500</t>
+          <t>400,500,600,700,800,900,1000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>300,350,400,450,500</t>
+          <t>600,700,800,900,1000</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>reward_reputation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>remark</t>
         </is>
       </c>
@@ -559,6 +564,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,6 +637,11 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>通关声望奖励(通关领奖后按冻结难度发放,需解锁研究100200011;单值=全难度共用,或与难度列表等长的逗号分隔逐难度值)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -694,6 +709,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>挑战100勇士-冒险者</t>
         </is>
       </c>
@@ -760,6 +780,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>4,5,6</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>挑战100勇士-持盾战士</t>
         </is>
       </c>
@@ -826,6 +851,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>挑战100勇士-弓箭手</t>
         </is>
       </c>
@@ -892,6 +922,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>挑战100勇士-强弓手</t>
         </is>
       </c>
@@ -958,6 +993,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>挑战100勇士-连射手</t>
         </is>
       </c>
@@ -1024,6 +1064,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-魔法师（火）</t>
         </is>
       </c>
@@ -1090,6 +1135,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-魔法师（水）</t>
         </is>
       </c>
@@ -1156,6 +1206,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-魔法师（冰）</t>
         </is>
       </c>
@@ -1222,6 +1277,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-魔法师（雷）</t>
         </is>
       </c>
@@ -1288,6 +1348,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>挑战100勇士-骷髅召唤师-小兵（无BOSS技能）</t>
         </is>
       </c>
@@ -1354,6 +1419,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>挑战100勇士-牧师</t>
         </is>
       </c>
@@ -1420,6 +1490,11 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>挑战100勇士-盗贼</t>
         </is>
       </c>
@@ -1486,6 +1561,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>挑战100勇士-大剑战士</t>
         </is>
       </c>
@@ -1552,6 +1632,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>挑战100勇士-大盾战士</t>
         </is>
       </c>
@@ -1618,6 +1703,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>挑战100勇士-持盾战士-Boss</t>
         </is>
       </c>
@@ -1684,6 +1774,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>挑战100勇士-强弓手-Boss</t>
         </is>
       </c>
@@ -1750,6 +1845,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>挑战100勇士-连射手-Boss</t>
         </is>
       </c>
@@ -1816,6 +1916,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-大魔法师（火）-BOSS</t>
         </is>
       </c>
@@ -1882,6 +1987,11 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>9,10</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>挑战100勇士-大魔导师（火冰水雷四系技能随机替代普攻,无普攻）-BOSS</t>
         </is>
       </c>
@@ -1948,6 +2058,11 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-大魔法师（水）-BOSS</t>
         </is>
       </c>
@@ -2014,6 +2129,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-大魔法师（冰）-BOSS</t>
         </is>
       </c>
@@ -2080,6 +2200,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>挑战100勇士-人类-大魔法师（雷）-BOSS</t>
         </is>
       </c>
@@ -2146,6 +2271,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>挑战100勇士-骷髅召唤师-BOSS</t>
         </is>
       </c>
@@ -2212,6 +2342,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>8,9,10</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>挑战100勇士-神官-BOSS</t>
         </is>
       </c>
@@ -2278,6 +2413,11 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>挑战100勇士-大剑战士-BOSS</t>
         </is>
       </c>
@@ -2344,6 +2484,11 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>挑战100勇士-勇者(BOSS)</t>
         </is>
       </c>
@@ -2410,6 +2555,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t>4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>挑战100勇士-大盾战士-BOSS</t>
         </is>
       </c>
@@ -2475,6 +2625,11 @@
         </is>
       </c>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>挑战100勇士-长枪骑士-BOSS</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_challenge_hundred_info[战斗-挑战100勇士].xlsx
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1,1.25</t>
+          <t>0.5,0.625</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.25,1.5,1.75,2</t>
+          <t>0.625,0.75,0.875,1</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.25,1.5,1.75,2</t>
+          <t>0.625,0.75,0.875,1</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5,1.75,2,2.5,3,3.5</t>
+          <t>0.75,0.875,1,1.25,1.5,1.75</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4,4.5</t>
+          <t>2,2.25</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5,1.75,2,2.5,3,3.5</t>
+          <t>0.75,0.875,1,1.25,1.5,1.75</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2,2.5,3,3.5</t>
+          <t>1,1.25,1.5,1.75</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2,2.5,3,3.5</t>
+          <t>1,1.25,1.5,1.75</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3,3.5,4,4.5</t>
+          <t>1.5,1.75,2,2.25</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.5,4,4.5</t>
+          <t>1.75,2,2.25</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.75,2,2.5,3,3.5,4,4.5</t>
+          <t>0.875,1,1.25,1.5,1.75,2,2.25</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.75,2,2.5,3,3.5,4,4.5</t>
+          <t>0.875,1,1.25,1.5,1.75,2,2.25</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.5,3,3.5,4,4.5</t>
+          <t>1.25,1.5,1.75,2,2.25</t>
         </is>
       </c>
       <c r="F31" t="n">
